--- a/data/Flow01/Fichier_erp.xlsx
+++ b/data/Flow01/Fichier_erp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TWB\Desktop\openClassrooms\Projet_10\data\Flow01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE14966-9C72-4A2E-AC75-4D2DA9073640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712600E5-ED3A-4DC0-90FE-1D3D72277BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2880" yWindow="11400" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-435" yWindow="13905" windowWidth="18900" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
